--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487423_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487423_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5159</v>
+        <v>4.2266</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7666</v>
+        <v>3.397</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7493</v>
+        <v>0.8295</v>
       </c>
       <c r="G2" t="n">
         <v>1.5981</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.16</v>
+        <v>0.5506</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5058</v>
+        <v>0.1247</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3458</v>
+        <v>0.426</v>
       </c>
       <c r="V2" t="n">
         <v>0.7069</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4992</v>
+        <v>1.9479</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5873</v>
+        <v>2.0093</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0881</v>
+        <v>-0.0614</v>
       </c>
       <c r="G3" t="n">
         <v>2.7302</v>
@@ -688,13 +688,13 @@
         <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5333</v>
+        <v>0.982</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2231</v>
+        <v>0.6452</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3101</v>
+        <v>0.3369</v>
       </c>
       <c r="V3" t="n">
         <v>-0.785</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2881</v>
+        <v>1.7881</v>
       </c>
       <c r="E4" t="n">
-        <v>1.19</v>
+        <v>1.5564</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.2318</v>
       </c>
       <c r="G4" t="n">
         <v>1.7674</v>
@@ -766,13 +766,13 @@
         <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6943</v>
+        <v>-0.1942</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8316</v>
+        <v>-0.4652</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1373</v>
+        <v>0.271</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1767</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9888</v>
+        <v>0.3144</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0326</v>
+        <v>-2.3827</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0214</v>
+        <v>2.6971</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7916</v>
+        <v>-0.5495</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5043</v>
+        <v>-2.0296</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7126</v>
+        <v>1.4802</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1416</v>
+        <v>-1.2004</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3032</v>
+        <v>-2.5129</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1617</v>
+        <v>1.3126</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3499</v>
+        <v>0.6509</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.201</v>
+        <v>0.4833</v>
       </c>
       <c r="O5" t="n">
-        <v>0.551</v>
+        <v>0.1676</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1145</v>
+        <v>0.665</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0882</v>
+        <v>-0.1294</v>
       </c>
       <c r="U5" t="n">
-        <v>2.0263</v>
+        <v>0.7944</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0576</v>
+        <v>0.9823</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.1014</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0576</v>
+        <v>-0.1191</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3639</v>
+        <v>0.0058</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6645</v>
+        <v>-0.5622</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3006</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>1.1889</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6887</v>
+        <v>-0.3191</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.594</v>
+        <v>-0.4917</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.1726</v>
       </c>
       <c r="V6" t="n">
         <v>0.1152</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3857</v>
+        <v>-0.199</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0561</v>
+        <v>-2.1779</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6704</v>
+        <v>1.9789</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5495</v>
+        <v>-0.7916</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0296</v>
+        <v>-1.5043</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4802</v>
+        <v>0.7126</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2004</v>
+        <v>-1.1416</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.5129</v>
+        <v>-1.3032</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3126</v>
+        <v>0.1617</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6509</v>
+        <v>0.3499</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4833</v>
+        <v>-0.201</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1676</v>
+        <v>0.551</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0351</v>
+        <v>0.9268</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8028</v>
+        <v>-0.0571</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7677</v>
+        <v>0.9838</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9823</v>
+        <v>0.0576</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1014</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1191</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PRIETO LORIENTE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6414</v>
+        <v>-0.2802</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3047</v>
+        <v>1.4509</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6633</v>
+        <v>-1.7311</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0075</v>
+        <v>2.5386</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4226</v>
+        <v>1.2957</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4301</v>
+        <v>1.2429</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4962</v>
+        <v>1.7126</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9528</v>
+        <v>1.0208</v>
       </c>
       <c r="L8" t="n">
-        <v>2.449</v>
+        <v>0.6919</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5113</v>
+        <v>0.826</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4698</v>
+        <v>0.275</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9811</v>
+        <v>0.551</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.1336</v>
+        <v>0.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1128</v>
+        <v>-0.1958</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3861</v>
+        <v>-0.1689</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.18</v>
+        <v>-0.0659</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5661</v>
+        <v>-0.1031</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09859999999999999</v>
+        <v>-3.0415</v>
       </c>
       <c r="W8" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3933</v>
+        <v>-3.0415</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>J. PRIETO LORIENTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8232</v>
+        <v>-0.4483</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0416</v>
+        <v>-1.2453</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8647</v>
+        <v>0.797</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5386</v>
+        <v>2.0075</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2957</v>
+        <v>-1.4226</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2429</v>
+        <v>3.4301</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7126</v>
+        <v>1.4962</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0208</v>
+        <v>-0.9528</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6919</v>
+        <v>2.449</v>
       </c>
       <c r="M9" t="n">
-        <v>0.826</v>
+        <v>0.5113</v>
       </c>
       <c r="N9" t="n">
-        <v>0.275</v>
+        <v>-0.4698</v>
       </c>
       <c r="O9" t="n">
-        <v>0.551</v>
+        <v>0.9811</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3917</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1958</v>
+        <v>-4.1128</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7119</v>
+        <v>0.5792</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4752</v>
+        <v>-0.1206</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2367</v>
+        <v>0.6997</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.0415</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0415</v>
+        <v>-1.3933</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ LUQUE</t>
+          <t>D. LASTRA GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0179</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.17</v>
+        <v>-0.7488</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8479</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5313</v>
+        <v>-0.5733</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6329</v>
+        <v>-0.6189</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1016</v>
+        <v>0.0456</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2386</v>
+        <v>0.1017</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2194</v>
+        <v>0.0612</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0193</v>
+        <v>0.0404</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2926</v>
+        <v>-0.675</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4135</v>
+        <v>-0.6802</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1209</v>
+        <v>0.0052</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3917</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4923</v>
+        <v>-0.055</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2952</v>
+        <v>0.1288</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1971</v>
+        <v>-0.1838</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. LASTRA GONZALEZ</t>
+          <t>G. RODRIGUEZ LUQUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.244</v>
+        <v>-1.1213</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1152</v>
+        <v>-0.4605</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1288</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5733</v>
+        <v>0.5313</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6189</v>
+        <v>0.6329</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0456</v>
+        <v>-0.1016</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1017</v>
+        <v>0.2386</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0612</v>
+        <v>0.2194</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0404</v>
+        <v>0.0193</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.675</v>
+        <v>0.2926</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6802</v>
+        <v>0.4135</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0052</v>
+        <v>-0.1209</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4749</v>
+        <v>0.3889</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2376</v>
+        <v>0.0047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2373</v>
+        <v>0.3842</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="12">
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.8159</v>
+        <v>5.409900000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2423999999999997</v>
+        <v>0.8361999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>4.5736</v>
+        <v>4.573599999999999</v>
       </c>
       <c r="G12" t="n">
         <v>10.4476</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.0674</v>
+        <v>-3.067399999999999</v>
       </c>
       <c r="I12" t="n">
         <v>13.5149</v>
@@ -1375,7 +1375,7 @@
         <v>2.5825</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3019999999999999</v>
+        <v>-0.302</v>
       </c>
       <c r="O12" t="n">
         <v>2.8848</v>
@@ -1390,13 +1390,13 @@
         <v>8.813000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7613</v>
+        <v>3.3553</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0205</v>
+        <v>-0.4265</v>
       </c>
       <c r="U12" t="n">
-        <v>3.7817</v>
+        <v>3.781699999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-4.4758</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5187</v>
+        <v>3.715</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8192</v>
+        <v>3.6145</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3005</v>
+        <v>0.1004</v>
       </c>
       <c r="G13" t="n">
         <v>3.0703</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9801</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4593</v>
+        <v>-0.664</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5208</v>
+        <v>-0.1198</v>
       </c>
       <c r="V13" t="n">
         <v>0.0576</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1138</v>
+        <v>2.0302</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2208</v>
+        <v>1.2441</v>
       </c>
       <c r="F14" t="n">
-        <v>0.893</v>
+        <v>0.7861</v>
       </c>
       <c r="G14" t="n">
         <v>-4.5872</v>
@@ -1546,13 +1546,13 @@
         <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5963</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.002</v>
+        <v>-0.9787</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4057</v>
+        <v>0.2988</v>
       </c>
       <c r="V14" t="n">
         <v>4.7512</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0237</v>
+        <v>0.1482</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5503</v>
+        <v>-0.3457</v>
       </c>
       <c r="F15" t="n">
-        <v>0.574</v>
+        <v>0.4938</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2969</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6587</v>
+        <v>-0.5342</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7128</v>
+        <v>-0.5082</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0542</v>
+        <v>-0.026</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>X. RUBIN CARBALLEIRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3979</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1525</v>
+        <v>-1.0386</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5504</v>
+        <v>0.2901</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0719</v>
+        <v>0.2781</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2488</v>
+        <v>0.1364</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1769</v>
+        <v>0.1416</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8387</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3593</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5206</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2332</v>
+        <v>0.2781</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8895</v>
+        <v>0.1364</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6563</v>
+        <v>0.1416</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5668</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0797</v>
+        <v>-0.0473</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0545</v>
+        <v>-0.0594</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0252</v>
+        <v>0.0121</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1578</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2178</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. RUBIN CARBALLEIRA</t>
+          <t>J. RODRIGUEZ BARRIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,22 +1735,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.802</v>
+        <v>-1.0149</v>
       </c>
       <c r="E17" t="n">
         <v>-1.0386</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2367</v>
+        <v>0.0238</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2781</v>
+        <v>-0.0625</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1364</v>
+        <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1416</v>
+        <v>-0.1313</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1762,13 +1762,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2781</v>
+        <v>-0.0625</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1364</v>
+        <v>0.0687</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1416</v>
+        <v>-0.1313</v>
       </c>
       <c r="P17" t="n">
         <v>-0.9792</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1008</v>
+        <v>0.0269</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0414</v>
+        <v>0.0863</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BARRIO</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9347</v>
+        <v>-1.3235</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0386</v>
+        <v>-0.6662</v>
       </c>
       <c r="F18" t="n">
-        <v>0.104</v>
+        <v>-0.6573</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0625</v>
+        <v>1.0719</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0687</v>
+        <v>2.2488</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1313</v>
+        <v>-1.1769</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.8387</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.3593</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5206</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0625</v>
+        <v>0.2332</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0687</v>
+        <v>0.8895</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1313</v>
+        <v>-0.6563</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9792</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1071</v>
+        <v>0.1541</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0594</v>
+        <v>0.2358</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1665</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.3756</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1402</v>
+        <v>-1.3449</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4506</v>
+        <v>0.246</v>
       </c>
       <c r="F19" t="n">
         <v>-1.5908</v>
@@ -1936,10 +1936,10 @@
         <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0529</v>
+        <v>-0.1517</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1623</v>
+        <v>-0.367</v>
       </c>
       <c r="U19" t="n">
         <v>0.2153</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7481</v>
+        <v>-2.4235</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1421</v>
+        <v>-2.6304</v>
       </c>
       <c r="F20" t="n">
-        <v>0.394</v>
+        <v>0.2069</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2736</v>
@@ -2014,13 +2014,13 @@
         <v>1.7626</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0205</v>
+        <v>-0.6959</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.7821</v>
+        <v>-1.2704</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.5745</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2166</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4493</v>
+        <v>-3.854</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.447</v>
+        <v>-3.9587</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0023</v>
+        <v>0.1046</v>
       </c>
       <c r="G21" t="n">
         <v>-5.6468</v>
@@ -2092,13 +2092,13 @@
         <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3553</v>
+        <v>-0.0494</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4011</v>
+        <v>-0.1106</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0457</v>
+        <v>0.0612</v>
       </c>
       <c r="V21" t="n">
         <v>0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.816</v>
+        <v>-4.8159</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5735</v>
+        <v>-4.5736</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2423000000000001</v>
+        <v>-0.2423999999999998</v>
       </c>
       <c r="G22" t="n">
         <v>-10.4475</v>
@@ -2146,7 +2146,7 @@
         <v>-2.5825</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3022</v>
+        <v>0.3022000000000002</v>
       </c>
       <c r="L22" t="n">
         <v>-2.8846</v>
@@ -2155,7 +2155,7 @@
         <v>-7.865</v>
       </c>
       <c r="N22" t="n">
-        <v>2.765200000000001</v>
+        <v>2.7652</v>
       </c>
       <c r="O22" t="n">
         <v>-10.6303</v>
@@ -2164,19 +2164,19 @@
         <v>3.9169</v>
       </c>
       <c r="Q22" t="n">
-        <v>-8.8131</v>
+        <v>-8.813099999999999</v>
       </c>
       <c r="R22" t="n">
         <v>12.7301</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.7614</v>
+        <v>-2.7612</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.781699999999999</v>
+        <v>-3.7819</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0206</v>
+        <v>1.0207</v>
       </c>
       <c r="V22" t="n">
         <v>4.476</v>
